--- a/WorkBot/refactor-experimental/data/orders/DUTCH VALLEY FOOD DIST/DUTCH VALLEY FOOD DIST_Bakery_20251116.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/DUTCH VALLEY FOOD DIST/DUTCH VALLEY FOOD DIST_Bakery_20251116.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +462,48 @@
       </c>
       <c r="E2" t="n">
         <v>87.90000000000001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>384097</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Oats</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="n">
+        <v>23.84</v>
+      </c>
+      <c r="E3" t="n">
+        <v>238.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>832400</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Register Tape - Thermal (3.125" x 230')</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>49.99</v>
+      </c>
+      <c r="E4" t="n">
+        <v>149.97</v>
       </c>
     </row>
   </sheetData>
